--- a/03_Entregables-diseño/SI - Ciclo II/2 - SI-IMPAMB - Controles de impactos ambientales/Instrumentos de evaluación/TC2/13_TC2_Rubrica.xlsx
+++ b/03_Entregables-diseño/SI - Ciclo II/2 - SI-IMPAMB - Controles de impactos ambientales/Instrumentos de evaluación/TC2/13_TC2_Rubrica.xlsx
@@ -82,7 +82,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -104,11 +104,55 @@
         <color rgb="009E9E9E"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009E9E9E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009E9E9E"/>
+      </right>
+      <top style="thin">
+        <color rgb="009E9E9E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="009E9E9E"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009E9E9E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="009E9E9E"/>
+      </right>
+      <top style="thin">
+        <color rgb="009E9E9E"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009E9E9E"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -149,6 +193,8 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,6 +577,11 @@
           <t>RÚBRICA DE EVALUACIÓN DE LA PRESENTACIÓN</t>
         </is>
       </c>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="15" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -553,6 +604,8 @@
           <t>Controles de impactos ambientales</t>
         </is>
       </c>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="15" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -575,6 +628,8 @@
           <t>Informe de descripción del manejo de residuos + anexo + PPT</t>
         </is>
       </c>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -582,6 +637,11 @@
           <t>La suma de los cinco criterios ES la nota vigesimal: 5 criterios × 4 puntos = 20.</t>
         </is>
       </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="5" t="inlineStr">
@@ -589,6 +649,9 @@
           <t>Excelente          ·          Bueno          ·          Regular          ·          En inicio</t>
         </is>
       </c>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -622,7 +685,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="78" customHeight="1">
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Comprensión del problema</t>
@@ -630,27 +693,149 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Describe qué residuos genera el taller y con qué cantidades, y clasifica cada uno en los dos ejes de la ley —peligroso o no peligroso, municipal o no municipal— sin confundirlos; ubica los residuos que el registro dejó en «varios».</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe los residuos que genera el taller, clasifica cada uno en los dos ejes de la ley </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>y ubica los que el registro dejó sin identificar.</t>
+          </r>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Describe y clasifica correctamente los residuos, pero no ubica los que quedaron sin identificar en el registro.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe los residuos que genera el taller y clasifica cada uno en </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">los dos ejes </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>de la ley.</t>
+          </r>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Clasifica en un solo eje, o confunde el eje de peligrosidad con el de competencia en más de un residuo.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe los residuos que genera el taller y clasifica </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">cada uno </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">en </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">un solo eje </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>de la ley.</t>
+          </r>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Enumera los residuos sin clasificarlos, o repite las cifras del registro sin decir qué tipo de residuo es cada una.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe los residuos que genera el taller y </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">no </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">clasifica </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">ninguno </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">en </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">los ejes </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>de la ley.</t>
+          </r>
         </is>
       </c>
       <c r="F8" s="9" t="n"/>
     </row>
-    <row r="9" ht="78" customHeight="1">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Desarrollo técnico</t>
@@ -658,106 +843,636 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Describe el manejo de cada residuo a lo largo de las operaciones, con la obligación que le aplica al generador en cada paso; describe qué código de colores le corresponde al taller y por qué es ese y no el otro; señala el plazo de almacenamiento que la norma fija para los peligrosos.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe el manejo de cada residuo con la obligación del generador, el código de colores que le toca al taller </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>y el plazo de almacenamiento.</t>
+          </r>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Describe el manejo y las obligaciones correctamente, pero no distingue qué código de colores le corresponde al taller, o no señala el plazo.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe el manejo de cada residuo con la obligación del generador </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">y </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">el código de colores </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>que le toca al taller.</t>
+          </r>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Describe el manejo en general sin ligarlo a la obligación del generador, o aplica el código de colores sin decir de dónde sale.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe el manejo de cada residuo </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">con </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">la obligación del generador, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">sin </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">el código de colores </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>ni el plazo.</t>
+          </r>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Menciona operaciones sueltas sin describir el manejo del residuo ni la obligación que le corresponde al generador.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe el manejo de cada residuo </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">sin </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">la obligación del generador </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">ni </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>el código de colores.</t>
+          </r>
         </is>
       </c>
       <c r="F9" s="9" t="n"/>
     </row>
-    <row r="10" ht="78" customHeight="1">
+    <row r="10" ht="54" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Conclusiones y análisis de resultados</t>
+          <t>Conclusiones</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Describe qué controles del taller no pueden sustentarse ante la verificación, señalando que la cadena documental del aceite queda incompleta porque el destino declarado no está autorizado para esa operación; describe qué le corresponde a cada residuo que quedó fuera.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe qué controles no pueden sustentarse, señala que el destino del aceite no está autorizado para esa operación </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>y dice qué le toca a cada residuo que quedó fuera.</t>
+          </r>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Describe los controles que fallan y señala el problema de la cadena documental, pero no describe qué le corresponde a los residuos que quedaron fuera.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe qué controles no pueden sustentarse y </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">señala que </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">el </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">destino </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">del aceite </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>no está autorizado para esa operación.</t>
+          </r>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Describe el manejo como conforme porque los documentos están firmados, sin contrastar lo que la constancia de registro autoriza.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe qué controles no pueden sustentarse y </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">revisa el manifiesto </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">del aceite </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>sin contrastarlo con lo que la constancia autoriza.</t>
+          </r>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Las conclusiones no distinguen lo que puede sustentarse de lo que no, o no se apoyan en los anexos.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Describe qué controles no pueden sustentarse y </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">da por buena la cadena </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">del aceite </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>porque los documentos están firmados.</t>
+          </r>
         </is>
       </c>
       <c r="F10" s="9" t="n"/>
     </row>
-    <row r="11" ht="78" customHeight="1">
+    <row r="11" ht="54" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Presentación PPT: contenido y diseño</t>
+          <t>Organización y presentación del producto</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>El PPT recorre las cinco láminas sin saltarse ninguna sección del informe; el registro y el manifiesto se muestran legibles y lo señalado se distingue a simple vista.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Cada lámina corresponde a una sección del producto y lleva su contenido en cuadro o esquema, con su sustento a la vista, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>y se entiende sin que el expositor la explique.</t>
+          </r>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Recorre las cinco láminas pero una queda apretada o ilegible.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Cada lámina corresponde a una sección del producto y lleva su contenido en </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">cuadro o esquema, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>con su sustento a la vista.</t>
+          </r>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Faltan dos o más láminas de contenido, o los anexos se proyectan ilegibles.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Cada lámina corresponde a una sección del producto y </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">lleva su contenido en texto corrido, con su </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>sustento a la vista.</t>
+          </r>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>El PPT reproduce los anexos copiados sin señalar nada, o no cubre el informe.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Cada lámina corresponde a una sección del producto y </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">vuelca sus párrafos, sin el </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>sustento a la vista.</t>
+          </r>
         </is>
       </c>
       <c r="F11" s="9" t="n"/>
     </row>
-    <row r="12" ht="78" customHeight="1">
+    <row r="12" ht="54" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Presentación oral: dominio y claridad</t>
+          <t>Sustentación oral</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Los cuatro integrantes exponen la parte que les tocó y responden la pregunta del instructor sobre una parte que no expusieron.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Todos los integrantes exponen la parte que les corresponde con orden y claridad, dentro del tiempo asignado, y </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">cualquiera </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">responde consultas </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>sobre una parte que no expuso.</t>
+          </r>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Los cuatro exponen su rol y el equipo responde, pero alguno no domina la parte ajena.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Todos los </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">integrantes exponen la parte que les corresponde con orden y claridad, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">dentro </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">del tiempo asignado, y el equipo responde </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">las </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>consultas del instructor.</t>
+          </r>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Algunos integrantes exponen con ideas sueltas o leyendo la lámina.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Algunos integrantes exponen </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">la parte que </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">les </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">corresponde </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">con orden y claridad, </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">se </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">pasan </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">del tiempo asignado, y el equipo responde </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">algunas </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t>consultas del instructor.</t>
+          </r>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Solo un integrante expone; el equipo no responde por las partes ajenas.</t>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Un integrante expone </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">la parte que </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">le </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">corresponde, se </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">pasa </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">del tiempo asignado, y el equipo responde </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">las </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">consultas del instructor </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>con imprecisión.</t>
+          </r>
         </is>
       </c>
       <c r="F12" s="9" t="n"/>
@@ -779,7 +1494,13 @@
           <t>NOTAS ESPECÍFICAS   ·   Excelente (4): está completo y correcto.   Bueno (3): completo con un fallo menor.   Regular (2): falta una pieza o hay confusión de fondo.   En inicio (1): no cumple lo que el criterio pide.</t>
         </is>
       </c>
-    </row>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="15" t="n"/>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
@@ -821,7 +1542,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>3 · Conclusiones y análisis de resultados</t>
+          <t>3 · Conclusiones</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -833,7 +1554,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>4 · Presentación PPT: contenido y diseño</t>
+          <t>4 · Organización y presentación del producto</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -845,7 +1566,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>5 · Presentación oral: dominio y claridad</t>
+          <t>5 · Sustentación oral</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -854,6 +1575,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
